--- a/data/trans_bre/P6904-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6904-Clase-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 16,93</t>
+          <t>-19,56; 18,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,9; 13,61</t>
+          <t>-28,58; 12,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 27,88</t>
+          <t>-14,75; 27,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 18,86</t>
+          <t>-15,69; 19,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 62,9</t>
+          <t>-46,22; 70,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-56,22; 40,73</t>
+          <t>-56,47; 36,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,22; 88,97</t>
+          <t>-26,06; 86,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 55,21</t>
+          <t>-28,36; 59,22</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 42,51</t>
+          <t>1,04; 40,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 1,49</t>
+          <t>-50,99; -0,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 34,06</t>
+          <t>-18,92; 35,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 23,31</t>
+          <t>-12,44; 27,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 341,66</t>
+          <t>3,5; 356,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,1; 9,04</t>
+          <t>-86,9; 9,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,12; 88,12</t>
+          <t>-28,32; 88,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 73,79</t>
+          <t>-24,91; 96,4</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-37,59; 15,91</t>
+          <t>-35,61; 14,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 26,03</t>
+          <t>-13,29; 26,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 43,16</t>
+          <t>-25,06; 39,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 35,25</t>
+          <t>-5,94; 34,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-57,13; 27,77</t>
+          <t>-52,84; 24,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 56,6</t>
+          <t>-22,55; 59,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-35,21; 85,47</t>
+          <t>-38,83; 76,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 67,64</t>
+          <t>-7,07; 67,69</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 14,11</t>
+          <t>-16,97; 13,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 9,0</t>
+          <t>-20,36; 10,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 19,65</t>
+          <t>-6,15; 19,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 5,76</t>
+          <t>-17,01; 7,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 25,54</t>
+          <t>-28,08; 25,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,67; 16,02</t>
+          <t>-31,12; 18,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 33,51</t>
+          <t>-8,98; 33,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 8,77</t>
+          <t>-23,82; 11,8</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 31,11</t>
+          <t>-3,55; 31,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 36,56</t>
+          <t>-10,89; 35,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 29,7</t>
+          <t>-6,17; 30,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 24,12</t>
+          <t>-10,39; 21,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 78,98</t>
+          <t>-5,92; 81,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 89,09</t>
+          <t>-15,6; 80,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 53,97</t>
+          <t>-8,27; 58,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 40,05</t>
+          <t>-12,38; 33,33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1112,42 +1112,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,17</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,65</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-5,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -1160,160 +1160,59 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,75; 8,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,66; 5,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,49; 16,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,44; 15,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-15,95; 17,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-20,07; 10,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,73; 29,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,35; 28,03</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,65</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,94%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-5,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-9,04; 7,74</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-12,72; 5,03</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,16; 16,18</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-4,05; 13,65</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-16,13; 15,39</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-22,0; 9,79</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-0,31; 29,22</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-6,14; 23,8</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>

--- a/data/trans_bre/P6904-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6904-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 18,45</t>
+          <t>-17,65; 17,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 12,3</t>
+          <t>-25,71; 15,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 27,43</t>
+          <t>-13,37; 27,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 19,45</t>
+          <t>-15,41; 21,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 70,41</t>
+          <t>-42,67; 70,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-56,47; 36,67</t>
+          <t>-52,41; 44,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 86,2</t>
+          <t>-25,24; 85,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 59,22</t>
+          <t>-28,04; 65,98</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,68</t>
+          <t>7,66</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 40,88</t>
+          <t>1,6; 41,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,99; -0,49</t>
+          <t>-50,91; -1,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 35,46</t>
+          <t>-15,59; 34,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 27,94</t>
+          <t>-12,06; 27,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 356,53</t>
+          <t>2,97; 360,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,9; 9,02</t>
+          <t>-85,88; 1,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 88,13</t>
+          <t>-23,8; 85,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 96,4</t>
+          <t>-22,78; 93,28</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,35</t>
+          <t>14,07</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-35,61; 14,43</t>
+          <t>-35,54; 18,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 26,97</t>
+          <t>-15,26; 28,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 39,58</t>
+          <t>-28,71; 37,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 34,67</t>
+          <t>-6,85; 33,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,84; 24,06</t>
+          <t>-53,36; 29,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 59,26</t>
+          <t>-25,94; 64,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 76,01</t>
+          <t>-50,33; 80,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 67,69</t>
+          <t>-9,84; 61,06</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,95</t>
+          <t>-7,78</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-8,81%</t>
+          <t>-11,28%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 13,87</t>
+          <t>-14,83; 14,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 10,8</t>
+          <t>-22,08; 9,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 19,34</t>
+          <t>-7,95; 18,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 7,4</t>
+          <t>-18,93; 4,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 25,16</t>
+          <t>-23,9; 28,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 18,9</t>
+          <t>-32,69; 17,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 33,95</t>
+          <t>-11,38; 30,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 11,8</t>
+          <t>-25,59; 6,77</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>-8,86</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>-10,91%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 31,64</t>
+          <t>-3,49; 32,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 35,31</t>
+          <t>-8,21; 36,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 30,02</t>
+          <t>-5,37; 29,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 21,57</t>
+          <t>-19,86; 4,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 81,74</t>
+          <t>-5,77; 82,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 80,97</t>
+          <t>-12,47; 81,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 58,35</t>
+          <t>-7,16; 54,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 33,33</t>
+          <t>-22,8; 6,7</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>-3,35%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 8,36</t>
+          <t>-8,72; 7,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 5,43</t>
+          <t>-12,06; 5,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 16,47</t>
+          <t>-1,05; 15,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 15,78</t>
+          <t>-8,83; 4,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 17,22</t>
+          <t>-15,42; 15,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 10,93</t>
+          <t>-20,8; 11,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 29,48</t>
+          <t>-1,7; 28,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 28,03</t>
+          <t>-13,45; 8,07</t>
         </is>
       </c>
     </row>
